--- a/artfynd/A 53145-2023 artfynd.xlsx
+++ b/artfynd/A 53145-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53145-2023 artfynd.xlsx
+++ b/artfynd/A 53145-2023 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>133414825</v>
       </c>
       <c r="B5" t="n">
-        <v>57947</v>
+        <v>57954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53145-2023 artfynd.xlsx
+++ b/artfynd/A 53145-2023 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>133414825</v>
       </c>
       <c r="B5" t="n">
-        <v>57954</v>
+        <v>57964</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53145-2023 artfynd.xlsx
+++ b/artfynd/A 53145-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106088955</v>
+        <v>37175356</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,27 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergebo, Dlr</t>
+          <t>Bergebo, Hönsarvet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525959.8989441213</v>
+        <v>525923</v>
       </c>
       <c r="R2" t="n">
-        <v>6708117.627314447</v>
+        <v>6708192</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2010-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2010-09-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög in i ett fönster vi Hagbacksgården.Vingskadad,kunde ej flyga.Infångades</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,77 +784,74 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Bengt Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114322612</v>
+        <v>40869387</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100034</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>sträckande SO</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergebo, Dlr</t>
+          <t>Bergebo, Hönsarvet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525960</v>
+        <v>525923</v>
       </c>
       <c r="R3" t="n">
-        <v>6708117</v>
+        <v>6708192</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2011-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2011-12-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,27 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Leif Carlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Leif Carlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114322620</v>
+        <v>23677620</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,27 +950,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergebo, Dlr</t>
+          <t>Bergebo, Hönsarvet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525960</v>
+        <v>525923</v>
       </c>
       <c r="R4" t="n">
-        <v>6708117</v>
+        <v>6708192</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2006-05-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2006-05-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,22 +1021,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133414825</v>
+        <v>68300061</v>
       </c>
       <c r="B5" t="n">
-        <v>57964</v>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,49 +1044,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102119</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergebo, Dlr</t>
+          <t>Bergebo, Hönsarvet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525960</v>
+        <v>525923</v>
       </c>
       <c r="R5" t="n">
-        <v>6708117</v>
+        <v>6708192</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1109,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2017-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2017-11-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst, hördes bara.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,6 +1153,4382 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>35221546</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S6" t="n">
+        <v>27</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-04-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-04-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skidstadion. Trummande</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>22948002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-03-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-03-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>106088955</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergebo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>525960</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6708117</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104423205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58435</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Möller</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Sandin, Patrik Engberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>22996964</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S10" t="n">
+        <v>27</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-04-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-04-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Utsiktspunkt, Bergebo.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>73745710</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Såg den under älgjakt var attackerad av en duvhök, efter fjärrvärme ledningen mot Falun.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åke Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åke Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102377559</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Cirklade några varv och gled sedan norrut</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>25131115</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-01-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-01-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Efter Igeltjärnsspåret. På samma ställe som förra året.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>30576989</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58018</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100094</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sommargylling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Oriolus oriolus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S14" t="n">
+        <v>27</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2008-06-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2008-06-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Inga-Lill Paulsen Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>37403515</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S15" t="n">
+        <v>27</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2010-10-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2010-10-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>51387715</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S16" t="n">
+        <v>27</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lilly Hansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lilly Hansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>39033716</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S17" t="n">
+        <v>27</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2011-05-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2011-05-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133414825</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57964</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergebo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>525960</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6708117</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>44411601</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S19" t="n">
+        <v>27</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2012-12-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2012-12-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Cirka. Vid skidstadion, troligtvis samma gäng som Patrik Engberg såg vid Medväga i torsdags</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22028850</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S20" t="n">
+        <v>27</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2005-12-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2005-12-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sågs sjunga längs skidspåret Igeltjärnsvägen</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Fridolfsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Fridolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22784687</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S21" t="n">
+        <v>27</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flög över skidspåret till Igeltjärn och satt sig i toppen på en liten gran. Fin skidobs!</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>32385205</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>27</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bergebo-Igeltjärn</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>32119789</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57238</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102972</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Turkduva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Streptopelia decaocto</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Frivaldszky, 1838)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S23" t="n">
+        <v>27</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2009-04-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2009-04-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Gällerspång</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Gällerspång</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>39466813</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S24" t="n">
+        <v>27</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Engberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Engberg, Emma Spåls</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>32258278</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S25" t="n">
+        <v>27</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2009-04-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2009-04-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anne Ristijärvi</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anne Ristijärvi</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>39457209</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S26" t="n">
+        <v>27</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Engberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Engberg, Emma Spåls</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25790904</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S27" t="n">
+        <v>27</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2007-03-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2007-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Vid Borlänge sjukhus</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Leif Carlberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Leif Carlberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>35236672</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S28" t="n">
+        <v>27</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2010-04-04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2010-04-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skidstadion</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>36538693</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S29" t="n">
+        <v>27</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skjutbanan</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Christer Bergström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Christer Bergström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>22410825</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S30" t="n">
+        <v>27</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Nils-Erik Björkbacka</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26251221</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S31" t="n">
+        <v>27</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2007-04-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2007-04-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Från Bergebo till Igeltjärn</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>39458404</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S32" t="n">
+        <v>27</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2011-06-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Engberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Engberg, Emma Spåls</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>26439257</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S33" t="n">
+        <v>27</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2007-05-06</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2007-05-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>22151075</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S34" t="n">
+        <v>27</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2005-11-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2005-11-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114322620</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergebo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>525960</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6708117</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>36556065</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S36" t="n">
+        <v>27</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2010-08-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Skjutbanan</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Christer Bergström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Christer Bergström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>22153217</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S37" t="n">
+        <v>27</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2005-11-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2005-11-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Yngve Johansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114322612</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bergebo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>525960</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6708117</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>65664667</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S39" t="n">
+        <v>27</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-05-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-05-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lilly Hansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lilly Hansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>32380751</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S40" t="n">
+        <v>27</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bergebo-Igeltjärn</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>32379607</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S41" t="n">
+        <v>27</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2009-04-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bergebo-Igeltjärn</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>114322626</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergebo, Hönsarvet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>525923</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S42" t="n">
+        <v>27</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53145-2023 artfynd.xlsx
+++ b/artfynd/A 53145-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37175356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/40869387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23677620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68300061</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1274,6 +1299,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/35221546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22948002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106088955</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104423205</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22996964</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1863,6 +1913,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73745710</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1979,6 +2034,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102377559</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2100,6 +2160,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25131115</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,6 +2281,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/30576989</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2337,6 +2407,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37403515</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2453,6 +2528,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/51387715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2569,6 +2649,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/39033716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2688,6 +2773,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133414825</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2809,6 +2899,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/44411601</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2940,6 +3035,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22028850</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3056,6 +3156,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22784687</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3177,6 +3282,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32385205</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3288,6 +3398,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32119789</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3404,6 +3519,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/39466813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3520,6 +3640,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32258278</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3636,6 +3761,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/39457209</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3757,6 +3887,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/25790904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3878,6 +4013,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/35236672</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4004,6 +4144,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/36538693</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4115,6 +4260,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22410825</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4241,6 +4391,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26251221</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4357,6 +4512,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/39458404</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4473,6 +4633,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26439257</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4584,6 +4749,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22151075</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4703,6 +4873,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114322620</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4824,6 +4999,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/36556065</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4935,6 +5115,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22153217</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5054,6 +5239,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114322612</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5168,6 +5358,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65664667</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5289,6 +5484,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32380751</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5410,6 +5610,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32379607</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5529,8 +5734,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114322626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>